--- a/artfynd/A 63151-2025 artfynd.xlsx
+++ b/artfynd/A 63151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88130177</v>
+        <v>88130179</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534293.9704674373</v>
+        <v>534301</v>
       </c>
       <c r="R2" t="n">
-        <v>7234070.071641969</v>
+        <v>7234072</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88130178</v>
+        <v>88130180</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>4404</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534298.1604963616</v>
+        <v>534251</v>
       </c>
       <c r="R3" t="n">
-        <v>7234070.959430069</v>
+        <v>7234099</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,19 +840,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88130176</v>
+        <v>88130177</v>
       </c>
       <c r="B4" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534225.8916171395</v>
+        <v>534294</v>
       </c>
       <c r="R4" t="n">
-        <v>7234109.136917252</v>
+        <v>7234070</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,19 +937,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88130179</v>
+        <v>88130178</v>
       </c>
       <c r="B5" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>534301.0905887285</v>
+        <v>534298</v>
       </c>
       <c r="R5" t="n">
-        <v>7234071.832574171</v>
+        <v>7234071</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,19 +1034,9 @@
           <t>2020-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1060,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88130176</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stennäs, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534226</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7234109</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-09-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emil Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emil Larsson, Carl Jansson, Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
